--- a/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.266706293162571</v>
+        <v>1.251067052233919</v>
       </c>
       <c r="C3" t="n">
-        <v>4.610293982437113</v>
+        <v>4.645568177450701</v>
       </c>
       <c r="D3" t="n">
-        <v>6.062915577450891</v>
+        <v>6.083404652038523</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93991585305057</v>
+        <v>11.98003988172314</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.410376932505716</v>
+        <v>1.370295097321335</v>
       </c>
       <c r="C4" t="n">
-        <v>5.067500122284127</v>
+        <v>5.163763663015151</v>
       </c>
       <c r="D4" t="n">
-        <v>6.374925951100701</v>
+        <v>6.350705424190222</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85280300589054</v>
+        <v>12.88476418452671</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.604088168771236</v>
+        <v>1.536981548367535</v>
       </c>
       <c r="C5" t="n">
-        <v>5.628346873696575</v>
+        <v>5.815782678717174</v>
       </c>
       <c r="D5" t="n">
-        <v>6.836983150280833</v>
+        <v>6.634808901904136</v>
       </c>
       <c r="E5" t="n">
-        <v>14.06941819274864</v>
+        <v>13.98757312898885</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.821732738248858</v>
+        <v>1.731344274017451</v>
       </c>
       <c r="C6" t="n">
-        <v>6.305859312247835</v>
+        <v>6.580431078775979</v>
       </c>
       <c r="D6" t="n">
-        <v>7.180112888710851</v>
+        <v>7.010931160189262</v>
       </c>
       <c r="E6" t="n">
-        <v>15.30770493920754</v>
+        <v>15.32270651298269</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.065270498543778</v>
+        <v>1.946074594637459</v>
       </c>
       <c r="C7" t="n">
-        <v>7.087768877599338</v>
+        <v>7.460516169457254</v>
       </c>
       <c r="D7" t="n">
-        <v>7.655677517043967</v>
+        <v>7.422374134724905</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80871689318708</v>
+        <v>16.82896489881962</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.28041427096398</v>
+        <v>1.179272355743113</v>
       </c>
       <c r="C8" t="n">
-        <v>4.706238945355411</v>
+        <v>5.065272282641843</v>
       </c>
       <c r="D8" t="n">
-        <v>5.938863848058888</v>
+        <v>5.803005356345333</v>
       </c>
       <c r="E8" t="n">
-        <v>11.92551706437828</v>
+        <v>12.04754999473029</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.607052432368259</v>
+        <v>1.473835427899032</v>
       </c>
       <c r="C9" t="n">
-        <v>5.651730554988031</v>
+        <v>6.165810554464345</v>
       </c>
       <c r="D9" t="n">
-        <v>6.513334089258551</v>
+        <v>6.342204920487511</v>
       </c>
       <c r="E9" t="n">
-        <v>13.77211707661484</v>
+        <v>13.98185090285089</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.953209956778981</v>
+        <v>1.790060582062094</v>
       </c>
       <c r="C10" t="n">
-        <v>6.724184236588317</v>
+        <v>7.419722351426453</v>
       </c>
       <c r="D10" t="n">
-        <v>7.033636108503482</v>
+        <v>6.952541614935777</v>
       </c>
       <c r="E10" t="n">
-        <v>15.71103030187078</v>
+        <v>16.16232454842432</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.299184909869254</v>
+        <v>2.1033053626112</v>
       </c>
       <c r="C11" t="n">
-        <v>7.901531454487779</v>
+        <v>8.805217415608789</v>
       </c>
       <c r="D11" t="n">
-        <v>7.569726912549383</v>
+        <v>7.510020588553356</v>
       </c>
       <c r="E11" t="n">
-        <v>17.77044327690642</v>
+        <v>18.41854336677335</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.6720147312093</v>
+        <v>2.435968515238302</v>
       </c>
       <c r="C12" t="n">
-        <v>9.150285581953986</v>
+        <v>10.22986312133034</v>
       </c>
       <c r="D12" t="n">
-        <v>8.088945361824395</v>
+        <v>8.035748729664355</v>
       </c>
       <c r="E12" t="n">
-        <v>19.91124567498768</v>
+        <v>20.701580366233</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.033925767091204</v>
+        <v>2.764114362737925</v>
       </c>
       <c r="C13" t="n">
-        <v>10.43848235115792</v>
+        <v>11.76375440352068</v>
       </c>
       <c r="D13" t="n">
-        <v>8.65418382866541</v>
+        <v>8.544975118860703</v>
       </c>
       <c r="E13" t="n">
-        <v>22.12659194691453</v>
+        <v>23.07284388511931</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.764907482878576</v>
+        <v>1.597568586689707</v>
       </c>
       <c r="C14" t="n">
-        <v>7.407600587807543</v>
+        <v>8.314696196623427</v>
       </c>
       <c r="D14" t="n">
-        <v>6.541453675735795</v>
+        <v>6.496411091064951</v>
       </c>
       <c r="E14" t="n">
-        <v>15.71396174642191</v>
+        <v>16.40867587437808</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.82287968481435</v>
+        <v>1.645438604748782</v>
       </c>
       <c r="C15" t="n">
-        <v>7.864672866473732</v>
+        <v>8.969816439667323</v>
       </c>
       <c r="D15" t="n">
-        <v>6.585170901005906</v>
+        <v>6.546539128843794</v>
       </c>
       <c r="E15" t="n">
-        <v>16.27272345229399</v>
+        <v>17.1617941732599</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.150508528675596</v>
+        <v>1.928820079579623</v>
       </c>
       <c r="C16" t="n">
-        <v>9.249801067441471</v>
+        <v>10.63191530295717</v>
       </c>
       <c r="D16" t="n">
-        <v>7.108255895305649</v>
+        <v>7.028969950710676</v>
       </c>
       <c r="E16" t="n">
-        <v>18.50856549142271</v>
+        <v>19.58970533324747</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.750829220799677</v>
+        <v>1.562156946997525</v>
       </c>
       <c r="C17" t="n">
-        <v>8.532654004443261</v>
+        <v>9.860389234620731</v>
       </c>
       <c r="D17" t="n">
-        <v>6.639471366527796</v>
+        <v>6.531204229703459</v>
       </c>
       <c r="E17" t="n">
-        <v>16.92295459177073</v>
+        <v>17.95375041132171</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.034564124804048</v>
+        <v>1.792808752633271</v>
       </c>
       <c r="C18" t="n">
-        <v>9.993062619372646</v>
+        <v>11.57596389536091</v>
       </c>
       <c r="D18" t="n">
-        <v>7.170783406589128</v>
+        <v>7.036617765326759</v>
       </c>
       <c r="E18" t="n">
-        <v>19.19841015076582</v>
+        <v>20.40539041332093</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.077888650992459</v>
+        <v>1.804295200772958</v>
       </c>
       <c r="C19" t="n">
-        <v>10.73611800428593</v>
+        <v>12.44693118866051</v>
       </c>
       <c r="D19" t="n">
-        <v>7.315964257093146</v>
+        <v>7.156606969739804</v>
       </c>
       <c r="E19" t="n">
-        <v>20.12997091237153</v>
+        <v>21.40783335917327</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.351982792541127</v>
+        <v>2.017943136171149</v>
       </c>
       <c r="C20" t="n">
-        <v>12.45387214492953</v>
+        <v>14.38093489611855</v>
       </c>
       <c r="D20" t="n">
-        <v>7.782687115692079</v>
+        <v>7.644447221457087</v>
       </c>
       <c r="E20" t="n">
-        <v>22.58854205316274</v>
+        <v>24.04332525374679</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.421040531989088</v>
+        <v>1.203917209717864</v>
       </c>
       <c r="C21" t="n">
-        <v>9.313457588584834</v>
+        <v>10.65395553891751</v>
       </c>
       <c r="D21" t="n">
-        <v>6.499150167159799</v>
+        <v>6.396969866101792</v>
       </c>
       <c r="E21" t="n">
-        <v>17.23364828773372</v>
+        <v>18.25484261473717</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251067052233919</v>
+        <v>1.264350098672378</v>
       </c>
       <c r="C3" t="n">
-        <v>4.645568177450701</v>
+        <v>4.645695804652253</v>
       </c>
       <c r="D3" t="n">
-        <v>6.083404652038523</v>
+        <v>6.12711205983159</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98003988172314</v>
+        <v>12.03715796315622</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370295097321335</v>
+        <v>1.401426341213315</v>
       </c>
       <c r="C4" t="n">
-        <v>5.163763663015151</v>
+        <v>5.178674227291468</v>
       </c>
       <c r="D4" t="n">
-        <v>6.350705424190222</v>
+        <v>6.407243122326416</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88476418452671</v>
+        <v>12.9873436908312</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.536981548367535</v>
+        <v>1.584663797776641</v>
       </c>
       <c r="C5" t="n">
-        <v>5.815782678717174</v>
+        <v>5.841264533816901</v>
       </c>
       <c r="D5" t="n">
-        <v>6.634808901904136</v>
+        <v>6.697595024222016</v>
       </c>
       <c r="E5" t="n">
-        <v>13.98757312898885</v>
+        <v>14.12352335581556</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.731344274017451</v>
+        <v>1.787332467777626</v>
       </c>
       <c r="C6" t="n">
-        <v>6.580431078775979</v>
+        <v>6.642711725464789</v>
       </c>
       <c r="D6" t="n">
-        <v>7.010931160189262</v>
+        <v>6.990611080370005</v>
       </c>
       <c r="E6" t="n">
-        <v>15.32270651298269</v>
+        <v>15.42065527361242</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.946074594637459</v>
+        <v>2.01243537942757</v>
       </c>
       <c r="C7" t="n">
-        <v>7.460516169457254</v>
+        <v>7.555149262852364</v>
       </c>
       <c r="D7" t="n">
-        <v>7.422374134724905</v>
+        <v>7.320146451605653</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82896489881962</v>
+        <v>16.88773109388559</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.179272355743113</v>
+        <v>1.218436549820653</v>
       </c>
       <c r="C8" t="n">
-        <v>5.065272282641843</v>
+        <v>5.14368128579182</v>
       </c>
       <c r="D8" t="n">
-        <v>5.803005356345333</v>
+        <v>5.616394095524567</v>
       </c>
       <c r="E8" t="n">
-        <v>12.04754999473029</v>
+        <v>11.97851193113704</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.473835427899032</v>
+        <v>1.506918223109197</v>
       </c>
       <c r="C9" t="n">
-        <v>6.165810554464345</v>
+        <v>6.264845858000085</v>
       </c>
       <c r="D9" t="n">
-        <v>6.342204920487511</v>
+        <v>6.160597635922517</v>
       </c>
       <c r="E9" t="n">
-        <v>13.98185090285089</v>
+        <v>13.9323617170318</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.790060582062094</v>
+        <v>1.807880834432296</v>
       </c>
       <c r="C10" t="n">
-        <v>7.419722351426453</v>
+        <v>7.506964092823672</v>
       </c>
       <c r="D10" t="n">
-        <v>6.952541614935777</v>
+        <v>6.751606107659089</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16232454842432</v>
+        <v>16.06645103491506</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.1033053626112</v>
+        <v>2.114496385264301</v>
       </c>
       <c r="C11" t="n">
-        <v>8.805217415608789</v>
+        <v>8.85965676296043</v>
       </c>
       <c r="D11" t="n">
-        <v>7.510020588553356</v>
+        <v>7.30858969421473</v>
       </c>
       <c r="E11" t="n">
-        <v>18.41854336677335</v>
+        <v>18.28274284243946</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.435968515238302</v>
+        <v>2.427780365586991</v>
       </c>
       <c r="C12" t="n">
-        <v>10.22986312133034</v>
+        <v>10.29121420781915</v>
       </c>
       <c r="D12" t="n">
-        <v>8.035748729664355</v>
+        <v>7.876139798114314</v>
       </c>
       <c r="E12" t="n">
-        <v>20.701580366233</v>
+        <v>20.59513437152045</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.764114362737925</v>
+        <v>2.724302176425447</v>
       </c>
       <c r="C13" t="n">
-        <v>11.76375440352068</v>
+        <v>11.76899926691784</v>
       </c>
       <c r="D13" t="n">
-        <v>8.544975118860703</v>
+        <v>8.520570420861183</v>
       </c>
       <c r="E13" t="n">
-        <v>23.07284388511931</v>
+        <v>23.01387186420447</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.597568586689707</v>
+        <v>1.585473454973386</v>
       </c>
       <c r="C14" t="n">
-        <v>8.314696196623427</v>
+        <v>8.322177114129786</v>
       </c>
       <c r="D14" t="n">
-        <v>6.496411091064951</v>
+        <v>6.511058766812313</v>
       </c>
       <c r="E14" t="n">
-        <v>16.40867587437808</v>
+        <v>16.41870933591549</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.645438604748782</v>
+        <v>1.600769084205552</v>
       </c>
       <c r="C15" t="n">
-        <v>8.969816439667323</v>
+        <v>8.900289067252563</v>
       </c>
       <c r="D15" t="n">
-        <v>6.546539128843794</v>
+        <v>6.60467822788929</v>
       </c>
       <c r="E15" t="n">
-        <v>17.1617941732599</v>
+        <v>17.10573637934741</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.928820079579623</v>
+        <v>1.845832946139641</v>
       </c>
       <c r="C16" t="n">
-        <v>10.63191530295717</v>
+        <v>10.43194311307914</v>
       </c>
       <c r="D16" t="n">
-        <v>7.028969950710676</v>
+        <v>7.117248704276548</v>
       </c>
       <c r="E16" t="n">
-        <v>19.58970533324747</v>
+        <v>19.39502476349533</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.562156946997525</v>
+        <v>1.46901854229563</v>
       </c>
       <c r="C17" t="n">
-        <v>9.860389234620731</v>
+        <v>9.521156132895291</v>
       </c>
       <c r="D17" t="n">
-        <v>6.531204229703459</v>
+        <v>6.671721778612304</v>
       </c>
       <c r="E17" t="n">
-        <v>17.95375041132171</v>
+        <v>17.66189645380322</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.792808752633271</v>
+        <v>1.66754756304842</v>
       </c>
       <c r="C18" t="n">
-        <v>11.57596389536091</v>
+        <v>11.0525647417958</v>
       </c>
       <c r="D18" t="n">
-        <v>7.036617765326759</v>
+        <v>7.176035756806847</v>
       </c>
       <c r="E18" t="n">
-        <v>20.40539041332093</v>
+        <v>19.89614806165107</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.804295200772958</v>
+        <v>1.667056689196296</v>
       </c>
       <c r="C19" t="n">
-        <v>12.44693118866051</v>
+        <v>11.75846097610335</v>
       </c>
       <c r="D19" t="n">
-        <v>7.156606969739804</v>
+        <v>7.341617324605116</v>
       </c>
       <c r="E19" t="n">
-        <v>21.40783335917327</v>
+        <v>20.76713498990476</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017943136171149</v>
+        <v>1.859361429504161</v>
       </c>
       <c r="C20" t="n">
-        <v>14.38093489611855</v>
+        <v>13.5872605995743</v>
       </c>
       <c r="D20" t="n">
-        <v>7.644447221457087</v>
+        <v>7.86880602430861</v>
       </c>
       <c r="E20" t="n">
-        <v>24.04332525374679</v>
+        <v>23.31542805338708</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.203917209717864</v>
+        <v>1.10887421446973</v>
       </c>
       <c r="C21" t="n">
-        <v>10.65395553891751</v>
+        <v>10.09163990635607</v>
       </c>
       <c r="D21" t="n">
-        <v>6.396969866101792</v>
+        <v>6.611255937507742</v>
       </c>
       <c r="E21" t="n">
-        <v>18.25484261473717</v>
+        <v>17.81177005833354</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_84_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264350098672378</v>
+        <v>2.592196342699765</v>
       </c>
       <c r="C3" t="n">
-        <v>4.645695804652253</v>
+        <v>7.742089017477979</v>
       </c>
       <c r="D3" t="n">
-        <v>6.12711205983159</v>
+        <v>8.15093848461248</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03715796315622</v>
+        <v>18.48522384479022</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.401426341213315</v>
+        <v>1.074347665993684</v>
       </c>
       <c r="C4" t="n">
-        <v>5.178674227291468</v>
+        <v>4.587351569143989</v>
       </c>
       <c r="D4" t="n">
-        <v>6.407243122326416</v>
+        <v>5.714665130346122</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9873436908312</v>
+        <v>11.37636436548379</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.584663797776641</v>
+        <v>1.170794312622387</v>
       </c>
       <c r="C5" t="n">
-        <v>5.841264533816901</v>
+        <v>5.346144606258235</v>
       </c>
       <c r="D5" t="n">
-        <v>6.697595024222016</v>
+        <v>5.965061663055612</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12352335581556</v>
+        <v>12.48200058193623</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.787332467777626</v>
+        <v>1.281122815152359</v>
       </c>
       <c r="C6" t="n">
-        <v>6.642711725464789</v>
+        <v>6.369061194882585</v>
       </c>
       <c r="D6" t="n">
-        <v>6.990611080370005</v>
+        <v>6.272366608474207</v>
       </c>
       <c r="E6" t="n">
-        <v>15.42065527361242</v>
+        <v>13.92255061850915</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.01243537942757</v>
+        <v>1.397685116081096</v>
       </c>
       <c r="C7" t="n">
-        <v>7.555149262852364</v>
+        <v>7.658630575803365</v>
       </c>
       <c r="D7" t="n">
-        <v>7.320146451605653</v>
+        <v>6.614511282416781</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88773109388559</v>
+        <v>15.67082697430124</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.218436549820653</v>
+        <v>1.51607841619857</v>
       </c>
       <c r="C8" t="n">
-        <v>5.14368128579182</v>
+        <v>9.156736922131943</v>
       </c>
       <c r="D8" t="n">
-        <v>5.616394095524567</v>
+        <v>6.990356535742984</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97851193113704</v>
+        <v>17.6631718740735</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.506918223109197</v>
+        <v>1.617387618050496</v>
       </c>
       <c r="C9" t="n">
-        <v>6.264845858000085</v>
+        <v>10.85324050238798</v>
       </c>
       <c r="D9" t="n">
-        <v>6.160597635922517</v>
+        <v>7.4460077850567</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9323617170318</v>
+        <v>19.91663590549518</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.807880834432296</v>
+        <v>1.010679809090964</v>
       </c>
       <c r="C10" t="n">
-        <v>7.506964092823672</v>
+        <v>7.903392995929225</v>
       </c>
       <c r="D10" t="n">
-        <v>6.751606107659089</v>
+        <v>5.862310066368979</v>
       </c>
       <c r="E10" t="n">
-        <v>16.06645103491506</v>
+        <v>14.77638287138917</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.114496385264301</v>
+        <v>0.9313055072026093</v>
       </c>
       <c r="C11" t="n">
-        <v>8.85965676296043</v>
+        <v>8.75226114840623</v>
       </c>
       <c r="D11" t="n">
-        <v>7.30858969421473</v>
+        <v>5.723520393419607</v>
       </c>
       <c r="E11" t="n">
-        <v>18.28274284243946</v>
+        <v>15.40708704902845</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.427780365586991</v>
+        <v>0.9886297556535807</v>
       </c>
       <c r="C12" t="n">
-        <v>10.29121420781915</v>
+        <v>10.65584049450967</v>
       </c>
       <c r="D12" t="n">
-        <v>7.876139798114314</v>
+        <v>6.165768281751667</v>
       </c>
       <c r="E12" t="n">
-        <v>20.59513437152045</v>
+        <v>17.81023853191492</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.724302176425447</v>
+        <v>0.7708584798975531</v>
       </c>
       <c r="C13" t="n">
-        <v>11.76899926691784</v>
+        <v>10.38245321130806</v>
       </c>
       <c r="D13" t="n">
-        <v>8.520570420861183</v>
+        <v>5.646266666572426</v>
       </c>
       <c r="E13" t="n">
-        <v>23.01387186420447</v>
+        <v>16.79957835777804</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.585473454973386</v>
+        <v>0.8184536085994384</v>
       </c>
       <c r="C14" t="n">
-        <v>8.322177114129786</v>
+        <v>12.3944076864833</v>
       </c>
       <c r="D14" t="n">
-        <v>6.511058766812313</v>
+        <v>5.99879263221337</v>
       </c>
       <c r="E14" t="n">
-        <v>16.41870933591549</v>
+        <v>19.21165392729611</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.600769084205552</v>
+        <v>0.7774460069930491</v>
       </c>
       <c r="C15" t="n">
-        <v>8.900289067252563</v>
+        <v>13.56623156374934</v>
       </c>
       <c r="D15" t="n">
-        <v>6.60467822788929</v>
+        <v>6.045278386009456</v>
       </c>
       <c r="E15" t="n">
-        <v>17.10573637934741</v>
+        <v>20.38895595675184</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.845832946139641</v>
+        <v>0.8321686240277664</v>
       </c>
       <c r="C16" t="n">
-        <v>10.43194311307914</v>
+        <v>15.81270593051506</v>
       </c>
       <c r="D16" t="n">
-        <v>7.117248704276548</v>
+        <v>6.500151549818132</v>
       </c>
       <c r="E16" t="n">
-        <v>19.39502476349533</v>
+        <v>23.14502610436096</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.46901854229563</v>
+        <v>0.4915905279475054</v>
       </c>
       <c r="C17" t="n">
-        <v>9.521156132895291</v>
+        <v>11.74820171259397</v>
       </c>
       <c r="D17" t="n">
-        <v>6.671721778612304</v>
+        <v>5.423056508534871</v>
       </c>
       <c r="E17" t="n">
-        <v>17.66189645380322</v>
+        <v>17.66284874907634</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.66754756304842</v>
+        <v>0.3758817435249763</v>
       </c>
       <c r="C18" t="n">
-        <v>11.0525647417958</v>
+        <v>10.68966170292097</v>
       </c>
       <c r="D18" t="n">
-        <v>7.176035756806847</v>
+        <v>4.981623470797335</v>
       </c>
       <c r="E18" t="n">
-        <v>19.89614806165107</v>
+        <v>16.04716691724328</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.667056689196296</v>
+        <v>0.4297502400569988</v>
       </c>
       <c r="C19" t="n">
-        <v>11.75846097610335</v>
+        <v>13.12366951615192</v>
       </c>
       <c r="D19" t="n">
-        <v>7.341617324605116</v>
+        <v>5.435328354837957</v>
       </c>
       <c r="E19" t="n">
-        <v>20.76713498990476</v>
+        <v>18.98874811104687</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.859361429504161</v>
+        <v>0.4793284991214627</v>
       </c>
       <c r="C20" t="n">
-        <v>13.5872605995743</v>
+        <v>15.67583066558897</v>
       </c>
       <c r="D20" t="n">
-        <v>7.86880602430861</v>
+        <v>5.891929394606106</v>
       </c>
       <c r="E20" t="n">
-        <v>23.31542805338708</v>
+        <v>22.04708855931654</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.10887421446973</v>
+        <v>0.5199924890313656</v>
       </c>
       <c r="C21" t="n">
-        <v>10.09163990635607</v>
+        <v>18.13952652939634</v>
       </c>
       <c r="D21" t="n">
-        <v>6.611255937507742</v>
+        <v>6.37807122279504</v>
       </c>
       <c r="E21" t="n">
-        <v>17.81177005833354</v>
+        <v>25.03759024122274</v>
       </c>
     </row>
   </sheetData>
